--- a/data/daily/2026-08/2026-08-27.xlsx
+++ b/data/daily/2026-08/2026-08-27.xlsx
@@ -1220,14 +1220,39 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="342900" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1242,17 +1267,67 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>4</row>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="342900" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="342900" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>7</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1267,17 +1342,17 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>5</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="323850" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
+      <row>8</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="342900" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1292,17 +1367,17 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>6</row>
+      <row>9</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId9"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1317,85 +1392,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>7</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="381000" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>8</row>
+      <row>10</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>9</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="9" name="Image 9" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>10</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -1475,77 +1475,152 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="1028700" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="1028700" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>6</col>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="866775" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>7</col>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -1553,104 +1628,29 @@
     <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>11</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1028700" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>9</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
     <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>10</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="9" name="Image 9" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>11</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1028700" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -2714,7 +2714,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>23,800원</t>
+          <t>21,900원</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -2836,7 +2836,7 @@
     <row r="11" ht="38" customHeight="1">
       <c r="B11" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -2844,27 +2844,27 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>비타민 선물 추천 아임비타 멀티비타민 이뮨샷 1박스(5입) / 비타민선물 응원선물 에너지 선물 직장동료 선물</t>
+          <t>오쏘몰 바이탈 m/f 남성/여성 선택가능 14입 - 시그니처 기프트 에디션 (공식수입)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>종근당건강</t>
+          <t>오쏘몰</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>15,900원</t>
+          <t>59,800원</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/5551542</t>
+          <t>https://gift.kakao.com/product/8167919</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260513082713_f5025425b9024348b2621639f67a34af.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260824090746_aecda274677840e2bce6fa7e201e1caa.jpg</t>
         </is>
       </c>
     </row>
@@ -2879,27 +2879,27 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>[헬로키티 한정판/단독] 리유저블백&amp;틴케이스 키링 증정, 엑스트라버진 올리브오일 캡슐 30포</t>
+          <t>[그레인온] 골드 카무트 브랜드밀효소G 3개월분+10포증정(총100포) + 파로저당단백칩 증정</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>푸드올로지</t>
+          <t>그레인온</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>29,900원</t>
+          <t>20,900원</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/11839566</t>
+          <t>https://gift.kakao.com/product/13180362</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260820175751_c5d7886f2f9642b8b4b4d5e38061f2bc.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260827152916_585042b9ed814333b774e55c37cb92ba.jpg</t>
         </is>
       </c>
     </row>
@@ -2941,7 +2941,7 @@
     <row r="14" ht="38" customHeight="1">
       <c r="B14" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -2949,34 +2949,34 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>[한끼통살] 닭가슴살 한달 식단패키지 30팩+(증정)보냉백</t>
+          <t>[헬로키티 한정판/단독] 리유저블백&amp;틴케이스 키링 증정, 엑스트라버진 올리브오일 캡슐 30포</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>한끼통살</t>
+          <t>푸드올로지</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>45,800원</t>
+          <t>29,900원</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/11566779</t>
+          <t>https://gift.kakao.com/product/11839566</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260429112212_3e1db89ad7174b6989286381ae7257c6.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260820175751_c5d7886f2f9642b8b4b4d5e38061f2bc.jpg</t>
         </is>
       </c>
     </row>
     <row r="15" ht="38" customHeight="1">
       <c r="B15" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -2984,34 +2984,34 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2입 추가 증정 "선물하기 1등 콜라겐" 아일로 타입1 콜라겐 비오틴 앰플 28일분 오간자 에디션+ 앰플 2입 추가 증정</t>
+          <t>[한끼통살] 닭가슴살 한달 식단패키지 30팩+(증정)보냉백</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>아일로</t>
+          <t>한끼통살</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>65,900원</t>
+          <t>45,800원</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/4965835</t>
+          <t>https://gift.kakao.com/product/11566779</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260703103417_e8e422c5cf9740e3bfc2662a9aaa1eef.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260429112212_3e1db89ad7174b6989286381ae7257c6.jpg</t>
         </is>
       </c>
     </row>
     <row r="16" ht="38" customHeight="1">
       <c r="B16" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -3019,27 +3019,27 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>[한끼통살] 단백질 든든형 닭가슴살 21일 식단관리+(증정)현미크리스피 닭가슴살 오리지널 1개</t>
+          <t>2입 추가 증정 "선물하기 1등 콜라겐" 아일로 타입1 콜라겐 비오틴 앰플 28일분 오간자 에디션+ 앰플 2입 추가 증정</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>한끼통살</t>
+          <t>아일로</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>32,900원</t>
+          <t>65,900원</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/12860133</t>
+          <t>https://gift.kakao.com/product/4965835</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260821134612_62bbe99621d6408d9e7e793b67d6e079.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260703103417_e8e422c5cf9740e3bfc2662a9aaa1eef.jpg</t>
         </is>
       </c>
     </row>
@@ -3054,27 +3054,27 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>아르기닌 증정 남친 활력선물 대한민국 NO.1 김종국 트리플아르기닌 6200 (30포) + 아르기닌 추가 증정</t>
+          <t>[한끼통살] 단백질 든든형 닭가슴살 21일 식단관리+(증정)현미크리스피 닭가슴살 오리지널 1개</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>익스트림</t>
+          <t>한끼통살</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>42,900원</t>
+          <t>32,900원</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/7417420</t>
+          <t>https://gift.kakao.com/product/12860133</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260706153340_3e124da6e254462d9a7efad2521e3b9e.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260821134612_62bbe99621d6408d9e7e793b67d6e079.jpg</t>
         </is>
       </c>
     </row>
@@ -3089,27 +3089,27 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>셀렉스 프로핏 맛있는 완전단백질 250ml 18팩 딸기초코/모카초콜릿/밀크바닐라/바나나 택1+베리오트바 2EA</t>
+          <t>아르기닌 증정 남친 활력선물 대한민국 NO.1 김종국 트리플아르기닌 6200 (30포) + 아르기닌 추가 증정</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>셀렉스</t>
+          <t>익스트림</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>27,900원</t>
+          <t>42,900원</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/13550266</t>
+          <t>https://gift.kakao.com/product/7417420</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260818144856_50ab1e34a7b8444cba1a8c0c7ec0ffce.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260706153340_3e124da6e254462d9a7efad2521e3b9e.jpg</t>
         </is>
       </c>
     </row>
@@ -3124,34 +3124,34 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>[운동선물/헬스] 삼대오백 모노 크레아틴 100서빙 운동 필수템 +키링증정</t>
+          <t>셀렉스 프로핏 맛있는 완전단백질 250ml 18팩 딸기초코/모카초콜릿/밀크바닐라/바나나 택1+베리오트바 2EA</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>삼대오백</t>
+          <t>셀렉스</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>17,900원</t>
+          <t>27,900원</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/6352718</t>
+          <t>https://gift.kakao.com/product/13550266</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260701120356_f9d975374d374b858dd4262325030e55.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260818144856_50ab1e34a7b8444cba1a8c0c7ec0ffce.jpg</t>
         </is>
       </c>
     </row>
     <row r="20" ht="38" customHeight="1">
       <c r="B20" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -3159,34 +3159,34 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>BEST 프로틴모음 [랩노쉬] 프로틴 락커 12종 선물세트 (프로틴 드링크 퍼펙트, 단백쿠키, 단백 쿠키바)</t>
+          <t>[운동선물/헬스] 삼대오백 모노 크레아틴 100서빙 운동 필수템 +키링증정</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>랩노쉬</t>
+          <t>삼대오백</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>20,900원</t>
+          <t>17,900원</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/12052312</t>
+          <t>https://gift.kakao.com/product/6352718</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260723171929_09161ef5007a47039ea2ea7988556deb.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260701120356_f9d975374d374b858dd4262325030e55.jpg</t>
         </is>
       </c>
     </row>
     <row r="21" ht="38" customHeight="1">
       <c r="B21" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -3194,27 +3194,27 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>"이게 바로 찐! 초고함량" 액상스틱 L-아르기닌 7000 3박스 [케이스 동봉]</t>
+          <t>BEST 프로틴모음 [랩노쉬] 프로틴 락커 12종 선물세트 (프로틴 드링크 퍼펙트, 단백쿠키, 단백 쿠키바)</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>뉴트리디데이</t>
+          <t>랩노쉬</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>30,900원</t>
+          <t>20,900원</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/4487367</t>
+          <t>https://gift.kakao.com/product/12052312</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260727151443_bd470867f85f4a79857e43d8b82ff835.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260723171929_09161ef5007a47039ea2ea7988556deb.jpg</t>
         </is>
       </c>
     </row>
@@ -3374,7 +3374,7 @@
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
     </row>
@@ -3431,7 +3431,7 @@
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>종근당건강</t>
+          <t>오쏘몰</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>비타민 선물 추천 아임비타 멀티비타민 이뮨샷 1박스(5입) / 비타민선물 응원선물 에너지 선물 직장동료 선물</t>
+          <t>오쏘몰 바이탈 m/f 남성/여성 선택가능 14입 - 시그니처 기프트 에디션 (공식수입)</t>
         </is>
       </c>
     </row>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>23,800원</t>
+          <t>21,900원</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>15,900원</t>
+          <t>59,800원</t>
         </is>
       </c>
     </row>
@@ -3698,42 +3698,42 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
           <t>다이어트/체중관리</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="G11" s="3" t="inlineStr">
         <is>
           <t>피부/미용</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="H11" s="3" t="inlineStr">
         <is>
           <t>다이어트/체중관리</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr">
+      <c r="I11" s="3" t="inlineStr">
         <is>
           <t>다이어트/체중관리</t>
         </is>
       </c>
-      <c r="I11" s="3" t="inlineStr">
+      <c r="J11" s="3" t="inlineStr">
         <is>
           <t>다이어트/체중관리</t>
         </is>
       </c>
-      <c r="J11" s="3" t="inlineStr">
+      <c r="K11" s="3" t="inlineStr">
         <is>
           <t>다이어트/체중관리</t>
         </is>
       </c>
-      <c r="K11" s="3" t="inlineStr">
+      <c r="L11" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="L11" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
         </is>
       </c>
     </row>
@@ -3745,52 +3745,52 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
+          <t>그레인온</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>그레인온</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
           <t>푸드올로지</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>그레인온</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="F12" s="3" t="inlineStr">
         <is>
           <t>한끼통살</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="G12" s="3" t="inlineStr">
         <is>
           <t>아일로</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="H12" s="3" t="inlineStr">
         <is>
           <t>한끼통살</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr">
+      <c r="I12" s="3" t="inlineStr">
         <is>
           <t>익스트림</t>
         </is>
       </c>
-      <c r="I12" s="3" t="inlineStr">
+      <c r="J12" s="3" t="inlineStr">
         <is>
           <t>셀렉스</t>
         </is>
       </c>
-      <c r="J12" s="3" t="inlineStr">
+      <c r="K12" s="3" t="inlineStr">
         <is>
           <t>삼대오백</t>
         </is>
       </c>
-      <c r="K12" s="3" t="inlineStr">
+      <c r="L12" s="3" t="inlineStr">
         <is>
           <t>랩노쉬</t>
-        </is>
-      </c>
-      <c r="L12" s="3" t="inlineStr">
-        <is>
-          <t>뉴트리디데이</t>
         </is>
       </c>
     </row>
@@ -3802,52 +3802,52 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
+          <t>[그레인온] 골드 카무트 브랜드밀효소G 3개월분+10포증정(총100포) + 파로저당단백칩 증정</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>[그레인온] 골드 카무트 브랜드밀 효소 3개월(+선물포장) +9포 추가 +파로저당 견과류바 +파로저당 단백칩 증정</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
           <t>[헬로키티 한정판/단독] 리유저블백&amp;틴케이스 키링 증정, 엑스트라버진 올리브오일 캡슐 30포</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>[그레인온] 골드 카무트 브랜드밀 효소 3개월(+선물포장) +9포 추가 +파로저당 견과류바 +파로저당 단백칩 증정</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t>[한끼통살] 닭가슴살 한달 식단패키지 30팩+(증정)보냉백</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="G13" s="3" t="inlineStr">
         <is>
           <t>2입 추가 증정 "선물하기 1등 콜라겐" 아일로 타입1 콜라겐 비오틴 앰플 28일분 오간자 에디션+ 앰플 2입 추가 증정</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="H13" s="3" t="inlineStr">
         <is>
           <t>[한끼통살] 단백질 든든형 닭가슴살 21일 식단관리+(증정)현미크리스피 닭가슴살 오리지널 1개</t>
         </is>
       </c>
-      <c r="H13" s="3" t="inlineStr">
+      <c r="I13" s="3" t="inlineStr">
         <is>
           <t>아르기닌 증정 남친 활력선물 대한민국 NO.1 김종국 트리플아르기닌 6200 (30포) + 아르기닌 추가 증정</t>
         </is>
       </c>
-      <c r="I13" s="3" t="inlineStr">
+      <c r="J13" s="3" t="inlineStr">
         <is>
           <t>셀렉스 프로핏 맛있는 완전단백질 250ml 18팩 딸기초코/모카초콜릿/밀크바닐라/바나나 택1+베리오트바 2EA</t>
         </is>
       </c>
-      <c r="J13" s="3" t="inlineStr">
+      <c r="K13" s="3" t="inlineStr">
         <is>
           <t>[운동선물/헬스] 삼대오백 모노 크레아틴 100서빙 운동 필수템 +키링증정</t>
         </is>
       </c>
-      <c r="K13" s="3" t="inlineStr">
+      <c r="L13" s="3" t="inlineStr">
         <is>
           <t>BEST 프로틴모음 [랩노쉬] 프로틴 락커 12종 선물세트 (프로틴 드링크 퍼펙트, 단백쿠키, 단백 쿠키바)</t>
-        </is>
-      </c>
-      <c r="L13" s="3" t="inlineStr">
-        <is>
-          <t>"이게 바로 찐! 초고함량" 액상스틱 L-아르기닌 7000 3박스 [케이스 동봉]</t>
         </is>
       </c>
     </row>
@@ -3859,52 +3859,52 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
+          <t>20,900원</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>45,900원</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
           <t>29,900원</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>45,900원</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="F14" s="3" t="inlineStr">
         <is>
           <t>45,800원</t>
         </is>
       </c>
-      <c r="F14" s="3" t="inlineStr">
+      <c r="G14" s="3" t="inlineStr">
         <is>
           <t>65,900원</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr">
+      <c r="H14" s="3" t="inlineStr">
         <is>
           <t>32,900원</t>
         </is>
       </c>
-      <c r="H14" s="3" t="inlineStr">
+      <c r="I14" s="3" t="inlineStr">
         <is>
           <t>42,900원</t>
         </is>
       </c>
-      <c r="I14" s="3" t="inlineStr">
+      <c r="J14" s="3" t="inlineStr">
         <is>
           <t>27,900원</t>
         </is>
       </c>
-      <c r="J14" s="3" t="inlineStr">
+      <c r="K14" s="3" t="inlineStr">
         <is>
           <t>17,900원</t>
         </is>
       </c>
-      <c r="K14" s="3" t="inlineStr">
+      <c r="L14" s="3" t="inlineStr">
         <is>
           <t>20,900원</t>
-        </is>
-      </c>
-      <c r="L14" s="3" t="inlineStr">
-        <is>
-          <t>30,900원</t>
         </is>
       </c>
     </row>
@@ -4089,7 +4089,7 @@
     <row r="3" ht="38" customHeight="1">
       <c r="B3" t="inlineStr">
         <is>
-          <t>홍삼/인삼</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -4097,12 +4097,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>자연관 홍삼정 에너타임 망고맛 14포 14일분</t>
+          <t>안국약품 브이팩 여성용 올인원 멀티 비타민 7포</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>자연관</t>
+          <t>안국약품</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -4112,19 +4112,19 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=901762104&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=968235548&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260612/M1nlLjjHeflYgIz5zIxp901762104_00_01M1nlLjjHeflYgIz5zIxp.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260402/05kyKLN3QpKvymmVHajT968235548_00_0005kyKLN3QpKvymmVHajT.jpg</t>
         </is>
       </c>
     </row>
     <row r="4" ht="38" customHeight="1">
       <c r="B4" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>비타민D</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -4132,34 +4132,34 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>비비랩 애사비 탱글 포켓 젤리 파인애플 5포 5일분</t>
+          <t>오브맘 비타민D＆아연 하루구미 30일분</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>비비랩 (BB LAB)</t>
+          <t>오브맘</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=994852702&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=613602130&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260615/bi8fBlec4ZBwEUtOa4Kz994852702_00_00bi8fBlec4ZBwEUtOa4Kz.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250922/dxtu28UFPhWKbi5IG3n8613602130_00_01dxtu28UFPhWKbi5IG3n8.jpg</t>
         </is>
       </c>
     </row>
     <row r="5" ht="38" customHeight="1">
       <c r="B5" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>마그네슘</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -4167,7 +4167,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>대웅제약 rTG 오메가3 30캡슐 30일분</t>
+          <t>대웅제약 마그네슘 샷 25ml x 5병 5일분</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -4182,19 +4182,19 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000145&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000204&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/OHEcumxqCcJ047eosRhh600000145_00_00OHEcumxqCcJ047eosRhh.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20251121/aHjoRwP9ejVVuu8M0Td4600000204_00_01aHjoRwP9ejVVuu8M0Td4.png</t>
         </is>
       </c>
     </row>
     <row r="6" ht="38" customHeight="1">
       <c r="B6" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -4202,7 +4202,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>동국제약 이너케어＆유산균 30캡슐</t>
+          <t>[신혜선 PICK] 동국제약 마데카 글루타치온 필름 12매 12일분</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610910677&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610911099&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250829/mBCVgsNacUdX2MZDROO3610910677_00_00mBCVgsNacUdX2MZDROO3.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260728/NbSqiy25P90IFlYxB3ux610911099_00_01NbSqiy25P90IFlYxB3ux.jpg</t>
         </is>
       </c>
     </row>
@@ -4237,12 +4237,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>휴럼 하루한포 유기농 야채분말 15포 15일분</t>
+          <t>닥터블릿 스트레스 케어 테아닌 30정 30일분</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>휴럼</t>
+          <t>닥터블릿</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -4252,19 +4252,19 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=919157056&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=286314466&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260706/z42ScLP7B6TWURzgDPY0919157056_00_01z42ScLP7B6TWURzgDPY0.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260805/2bO6NPfrJW4dB8O5FDEz286314466_00_002bO6NPfrJW4dB8O5FDEz.png</t>
         </is>
       </c>
     </row>
     <row r="8" ht="38" customHeight="1">
       <c r="B8" t="inlineStr">
         <is>
-          <t>비타민D</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -4272,7 +4272,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>대웅제약 비타민D 4000IU 30정 30일분</t>
+          <t>대웅제약 밀크씨슬 에너지샷 5포</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -4282,24 +4282,24 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000132&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000197&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/SvY5chCvz0QZIyP7AdTc600000132_00_00SvY5chCvz0QZIyP7AdTc.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250813/V9qCJdlaEC8Ugb1xrzDE600000197_00_00V9qCJdlaEC8Ugb1xrzDE.png</t>
         </is>
       </c>
     </row>
     <row r="9" ht="38" customHeight="1">
       <c r="B9" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -4307,34 +4307,34 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>동국 맛있는 센시안 브이캔디 20정 20일분</t>
+          <t>영진 비타민C 츄어블 12정</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>영진약품</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>1,000원</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610910968&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=286314181&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260409/2cHZmOZUJJcZL1ip2bls610910968_00_002cHZmOZUJJcZL1ip2bls.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260310/OAO3HGgecCtu4XcRrckd286314181_00_01OAO3HGgecCtu4XcRrckd.jpg</t>
         </is>
       </c>
     </row>
     <row r="10" ht="38" customHeight="1">
       <c r="B10" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -4342,34 +4342,34 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>[신혜선 PICK] 동국 마이팝 발효효소＆매실</t>
+          <t>LG생활건강 이너뷰 진한 레드 석류 콜라겐 7포</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>이너뷰 바이 리튠</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610911031&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=994953529&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260623/AwS7hZ6EGxkGDWyKLCd8610911031_00_00AwS7hZ6EGxkGDWyKLCd8.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250627/vXg1N5D0xbSNweDPvvl2994953529_00_00vXg1N5D0xbSNweDPvvl2.jpg</t>
         </is>
       </c>
     </row>
     <row r="11" ht="38" customHeight="1">
       <c r="B11" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -4377,27 +4377,27 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>대웅제약 루테인 30정 30일분</t>
+          <t>닥터블릿 푸응 7days 팻버닝 21캡슐</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>닥터블릿</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000126&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=613602085&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/u8Kxfk5gV3uvRKBRNTM6600000126_00_00u8Kxfk5gV3uvRKBRNTM6.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260624/m6tznB24o1VYvw4vwVs3613602085_00_00m6tznB24o1VYvw4vwVs3.jpg</t>
         </is>
       </c>
     </row>
@@ -4517,24 +4517,24 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>홍삼/인삼</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
+          <t>비타민D</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>마그네슘</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>루테인/눈건강</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>프로바이오틱스/유산균</t>
-        </is>
-      </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
@@ -4542,22 +4542,22 @@
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>비타민D</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
+          <t>비타민C/항산화</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>피부/미용</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
           <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>루테인/눈건강</t>
         </is>
       </c>
     </row>
@@ -4574,12 +4574,12 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>자연관</t>
+          <t>안국약품</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>비비랩 (BB LAB)</t>
+          <t>오브맘</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>휴럼</t>
+          <t>닥터블릿</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
@@ -4604,17 +4604,17 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>영진약품</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>이너뷰 바이 리튠</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>닥터블릿</t>
         </is>
       </c>
     </row>
@@ -4631,47 +4631,47 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>자연관 홍삼정 에너타임 망고맛 14포 14일분</t>
+          <t>안국약품 브이팩 여성용 올인원 멀티 비타민 7포</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>비비랩 애사비 탱글 포켓 젤리 파인애플 5포 5일분</t>
+          <t>오브맘 비타민D＆아연 하루구미 30일분</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 rTG 오메가3 30캡슐 30일분</t>
+          <t>대웅제약 마그네슘 샷 25ml x 5병 5일분</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>동국제약 이너케어＆유산균 30캡슐</t>
+          <t>[신혜선 PICK] 동국제약 마데카 글루타치온 필름 12매 12일분</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>휴럼 하루한포 유기농 야채분말 15포 15일분</t>
+          <t>닥터블릿 스트레스 케어 테아닌 30정 30일분</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 비타민D 4000IU 30정 30일분</t>
+          <t>대웅제약 밀크씨슬 에너지샷 5포</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>동국 맛있는 센시안 브이캔디 20정 20일분</t>
+          <t>영진 비타민C 츄어블 12정</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>[신혜선 PICK] 동국 마이팝 발효효소＆매실</t>
+          <t>LG생활건강 이너뷰 진한 레드 석류 콜라겐 7포</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 루테인 30정 30일분</t>
+          <t>닥터블릿 푸응 7days 팻버닝 21캡슐</t>
         </is>
       </c>
     </row>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
@@ -4713,22 +4713,22 @@
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>1,000원</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>2,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
     </row>
@@ -4867,7 +4867,7 @@
     <row r="2" ht="38" customHeight="1">
       <c r="B2" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -4875,34 +4875,34 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>고려은단 비타민C1000 600정 (20개월분)</t>
+          <t>[8월 올영픽/덴프스] 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>고려은단</t>
+          <t>덴프스</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>42,900원</t>
+          <t>31,300원</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000225938&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=1</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000202658&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=1</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022593803ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020265832ko.jpg?l=ko</t>
         </is>
       </c>
     </row>
     <row r="3" ht="38" customHeight="1">
       <c r="B3" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -4910,34 +4910,34 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>[8월 올영픽/한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
+          <t>[8월올영픽+더블증정] 셀트리온 홀드잇 매드 MAD 10+2정 (+2정 온라인)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>프로뉴트리션</t>
+          <t>이너랩</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>32,900원</t>
+          <t>17,910원</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000205496&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=2</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000254467&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=2</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020549616ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0025/A00000025446725ko.png?l=ko</t>
         </is>
       </c>
     </row>
     <row r="4" ht="38" customHeight="1">
       <c r="B4" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -4945,34 +4945,34 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>[8월 올영픽/덴프스] 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
+          <t>[8월 올영픽] 오쏘몰 이뮨 멀티비타민&amp;미네랄 14+1입</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>덴프스</t>
+          <t>오쏘몰</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>31,300원</t>
+          <t>49,900원</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000202658&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=3</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000193086&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=3</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020265832ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0019/A00000019308653ko.jpg?l=ko</t>
         </is>
       </c>
     </row>
     <row r="5" ht="38" customHeight="1">
       <c r="B5" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -4980,34 +4980,34 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>[8월올영픽+더블증정] 셀트리온 홀드잇 매드 MAD 10+2정 (+2정 온라인)</t>
+          <t>[8월 올영픽/파격특가] 콜레올로지 컷팅 젤리 레몬/키위/석류 10+2+2포 기획 외</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>이너랩</t>
+          <t>푸드올로지</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>17,910원</t>
+          <t>11,900원</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000254467&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=4</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000183645&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=4</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0025/A00000025446725ko.png?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0018/A00000018364585ko.jpg?l=ko</t>
         </is>
       </c>
     </row>
     <row r="6" ht="38" customHeight="1">
       <c r="B6" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -5015,34 +5015,34 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>[8월 올영픽] 오쏘몰 이뮨 멀티비타민&amp;미네랄 14+1입</t>
+          <t>[8월 올영픽/곽민경 PICK] 생활약속 기분전환 알파플러스 10포 (+1포 증정기획)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>오쏘몰</t>
+          <t>생활약속</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>49,900원</t>
+          <t>14,500원</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000193086&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=5</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000180121&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=5</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0019/A00000019308653ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0018/A00000018012131ko.jpg?l=ko</t>
         </is>
       </c>
     </row>
     <row r="7" ht="38" customHeight="1">
       <c r="B7" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -5050,27 +5050,27 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>오쏘몰 이뮨 멀티비타민&amp;미네랄 14+1입 (15일분)</t>
+          <t>[8월 올영픽/한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>오쏘몰</t>
+          <t>프로뉴트리션</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>49,900원</t>
+          <t>32,900원</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000149568&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000205496&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0014/A00000014956815ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020549616ko.jpg?l=ko</t>
         </is>
       </c>
     </row>
@@ -5120,34 +5120,34 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>[8월 올영픽/곽민경 PICK] 생활약속 기분전환 알파플러스 10포 (+1포 증정기획)</t>
+          <t>[8월올영픽]올더베러 웰니스 구미 30일분 택1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>생활약속</t>
+          <t>올더베러</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>14,500원</t>
+          <t>10,900원</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000180121&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=8</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000245874&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=8</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0018/A00000018012131ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024587415ko.jpg?l=ko</t>
         </is>
       </c>
     </row>
     <row r="10" ht="38" customHeight="1">
       <c r="B10" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -5155,34 +5155,34 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>[올영단독][키위맛 곤약쌀 젤리] 셀트리온 홀드잇 Jelly 포켓 젤리 10일분(+2일분)</t>
+          <t>오쏘몰 이뮨 멀티비타민&amp;미네랄 14+1입 (15일분)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>이너랩</t>
+          <t>오쏘몰</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>14,900원</t>
+          <t>49,900원</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000254481&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000149568&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0025/A00000025448122ko.png?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0014/A00000014956816ko.jpg?l=ko</t>
         </is>
       </c>
     </row>
     <row r="11" ht="38" customHeight="1">
       <c r="B11" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -5190,27 +5190,27 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
+          <t>[8월 올영픽/감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>지노마스터</t>
+          <t>멜라메이트</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>27,400원</t>
+          <t>16,900원</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000244929&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000223554&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024492930ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022355463ko.jpg?l=ko</t>
         </is>
       </c>
     </row>
@@ -5325,52 +5325,52 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>멀티비타민/종합비타민</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
           <t>다이어트/체중관리</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>프로바이오틱스/유산균</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>멀티비타민/종합비타민</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>멀티비타민/종합비타민</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
     </row>
@@ -5382,52 +5382,52 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>고려은단</t>
+          <t>덴프스</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
+          <t>이너랩</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>오쏘몰</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>푸드올로지</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>생활약속</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
           <t>프로뉴트리션</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>덴프스</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>이너랩</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>대원제약</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>올더베러</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>오쏘몰</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>오쏘몰</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>대원제약</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>생활약속</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>이너랩</t>
-        </is>
-      </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>지노마스터</t>
+          <t>멜라메이트</t>
         </is>
       </c>
     </row>
@@ -5439,52 +5439,52 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>고려은단 비타민C1000 600정 (20개월분)</t>
+          <t>[8월 올영픽/덴프스] 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
+          <t>[8월올영픽+더블증정] 셀트리온 홀드잇 매드 MAD 10+2정 (+2정 온라인)</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>[8월 올영픽] 오쏘몰 이뮨 멀티비타민&amp;미네랄 14+1입</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>[8월 올영픽/파격특가] 콜레올로지 컷팅 젤리 레몬/키위/석류 10+2+2포 기획 외</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>[8월 올영픽/곽민경 PICK] 생활약속 기분전환 알파플러스 10포 (+1포 증정기획)</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
           <t>[8월 올영픽/한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>[8월 올영픽/덴프스] 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>[8월올영픽+더블증정] 셀트리온 홀드잇 매드 MAD 10+2정 (+2정 온라인)</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>[8월 올영픽] 오쏘몰 이뮨 멀티비타민&amp;미네랄 14+1입</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>[8월 올영픽/수면 효율증가]대원제약 대원헬스 꿀잠샷 20gX12포 (+2포+수면안대) (14일분)</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>[8월올영픽]올더베러 웰니스 구미 30일분 택1</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
         <is>
           <t>오쏘몰 이뮨 멀티비타민&amp;미네랄 14+1입 (15일분)</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>[8월 올영픽/수면 효율증가]대원제약 대원헬스 꿀잠샷 20gX12포 (+2포+수면안대) (14일분)</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>[8월 올영픽/곽민경 PICK] 생활약속 기분전환 알파플러스 10포 (+1포 증정기획)</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>[올영단독][키위맛 곤약쌀 젤리] 셀트리온 홀드잇 Jelly 포켓 젤리 10일분(+2일분)</t>
-        </is>
-      </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
+          <t>[8월 올영픽/감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
         </is>
       </c>
     </row>
@@ -5496,52 +5496,52 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>42,900원</t>
+          <t>31,300원</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
+          <t>17,910원</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>49,900원</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>11,900원</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>14,500원</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
           <t>32,900원</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>31,300원</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>17,910원</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>17,800원</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>10,900원</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
         <is>
           <t>49,900원</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>49,900원</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>17,800원</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>14,500원</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>14,900원</t>
-        </is>
-      </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>27,400원</t>
+          <t>16,900원</t>
         </is>
       </c>
     </row>
@@ -5671,19 +5671,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C2" t="n">
-        <v>30</v>
+        <v>37.5</v>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E2" t="n">
         <v>5</v>
       </c>
       <c r="F2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -5699,10 +5699,10 @@
         <v>27.5</v>
       </c>
       <c r="D3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
         <v>2</v>
@@ -5721,54 +5721,54 @@
         <v>17.5</v>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C5" t="n">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>홍삼/인삼</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="n">
         <v>0</v>
-      </c>
-      <c r="E6" t="n">
-        <v>2</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -5777,17 +5777,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>홍삼/인삼</t>
+          <t>마그네슘</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
@@ -5821,7 +5821,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -5831,10 +5831,10 @@
         <v>2.5</v>
       </c>
       <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
         <v>1</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -5843,7 +5843,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="B10" t="n">
